--- a/emc/dist/20261025_台光電模型_v0.2.xlsx
+++ b/emc/dist/20261025_台光電模型_v0.2.xlsx
@@ -6184,7 +6184,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6421,7 +6421,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6542,7 +6542,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6663,7 +6663,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6784,7 +6784,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6905,7 +6905,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
